--- a/AAII_Financials/Quarterly/KLAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KLAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>KLAC</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3657600</v>
+      </c>
+      <c r="E8" s="3">
         <v>3415100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3297100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3209700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3174700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3063000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3076900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2841500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2568700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2359800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2486700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2397000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2355100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2432600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2983900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2724400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2486700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2288700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2352600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2083800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1925500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1803800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1650900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1538600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1459600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1424000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1509500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1413400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1258400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1097300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1119900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1093300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1070000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1021300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>975800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>969600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>938600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>913800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>876900</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>750700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1413100</v>
+      </c>
+      <c r="E9" s="3">
         <v>1327700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1271200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1243100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1207300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1175700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1221500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1147400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1010600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>993900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>976700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>946900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>962900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1005300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1167900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>994700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>933500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>849400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>867100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>772700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>772300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>709400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>669700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>583700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>621500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>590200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>633600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>602400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>593800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>486900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>408100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>381300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>377700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>368100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>347000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>352500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>347800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>343600</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>318500</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>277900</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2244400</v>
+      </c>
+      <c r="E10" s="3">
         <v>2087400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2025900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1966600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1967500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1887300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1855400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1694100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1558200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1365900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1510000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1450100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1392200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1427300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1816000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1729700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1553200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1439300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1485500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1311100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1153200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1094400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>981200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>954900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>838100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>833800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>875900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>811000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>664600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>610400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>711800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>712000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>692300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>653200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>628800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>617100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>590800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>570200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>558400</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>472800</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,130 +1248,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>399000</v>
+      </c>
+      <c r="E12" s="3">
         <v>388800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>383900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>360500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>353000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>338000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>346200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>323100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>325800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>321600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>320400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>311200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>317100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>328300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>332800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>318500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>296900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>285200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>265000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>258100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>241400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>238900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>229000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>219000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>217100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>215400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>220600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>210500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>206700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>184900</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>165900</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>153500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>152000</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>153300</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>156700</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>146700</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>136600</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>130200</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>130900</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>129200</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1479,88 +1496,91 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-32100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5400</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-100</v>
       </c>
       <c r="G14" s="3">
         <v>-100</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>239100</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>70400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>219100</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>40800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>59800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>45100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>42700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>41100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>40900</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>36900</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>279200</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>10</v>
@@ -1577,11 +1597,11 @@
       <c r="AH14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AI14" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
       </c>
       <c r="AK14" s="3" t="s">
         <v>10</v>
@@ -1589,11 +1609,11 @@
       <c r="AL14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AM14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="3" t="s">
+      <c r="AM14" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="AN14" s="3">
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="s">
         <v>10</v>
@@ -1601,52 +1621,55 @@
       <c r="AP14" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>98600</v>
+      </c>
+      <c r="E15" s="3">
         <v>99100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>99300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>97000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>96300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>98100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>103900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>95800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>101000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>99300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>99100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>102400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>104800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>104900</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>20200</v>
       </c>
       <c r="R15" s="3">
         <v>20200</v>
@@ -1655,46 +1678,46 @@
         <v>20200</v>
       </c>
       <c r="T15" s="3">
+        <v>20200</v>
+      </c>
+      <c r="U15" s="3">
         <v>15100</v>
-      </c>
-      <c r="U15" s="3">
-        <v>12400</v>
       </c>
       <c r="V15" s="3">
         <v>12400</v>
       </c>
       <c r="W15" s="3">
+        <v>12400</v>
+      </c>
+      <c r="X15" s="3">
         <v>11800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>12100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>12300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>13500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>14300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>17800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>20400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>22300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>24000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>10100</v>
-      </c>
-      <c r="AG15" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AH15" s="3" t="s">
         <v>10</v>
@@ -1702,8 +1725,8 @@
       <c r="AI15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AJ15" s="3">
-        <v>0</v>
+      <c r="AJ15" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AK15" s="3">
         <v>0</v>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2103600</v>
+      </c>
+      <c r="E17" s="3">
         <v>2007600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1935000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1872500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1823000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1762600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1834700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1721600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1591400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1553000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1534400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1497800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1533800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1572000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1784700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1627000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1512200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1393800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1386700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1265000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1205700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1131600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1080700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1012200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1006400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1270500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1046600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1003200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>989500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>854000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>686600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>649400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>646500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>635500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>609600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>607900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>589600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>569700</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>543000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>501500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1553900</v>
+      </c>
+      <c r="E18" s="3">
         <v>1407500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1362100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1337200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1351800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1300400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1242200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1119900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>977300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>806800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>952300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>899200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>821300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>860600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1199200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1097400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>974500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>894900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>965900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>818800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>719800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>672200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>570200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>526400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>453200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>153500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>462900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>410200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>268900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>243300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>433300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>443900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>423500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>385800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>366200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>361700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>349000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>344100</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>333900</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>249200</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,618 +2085,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-47600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-43200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-43300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>130200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-35900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-44500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-40900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>110000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-45600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-32200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-26800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>46300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>18100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>47000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>19400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-8700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-14100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>29000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>7300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-7900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>3000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>9300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>9200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>10000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>11300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>8300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>8500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>5000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>6700</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>5500</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>3500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1579200</v>
+      </c>
+      <c r="E21" s="3">
         <v>1554200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1504600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1477500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1317900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1434400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1390500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1256700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>968300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>951700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1083600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1028400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>879900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>980600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1320800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1246400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1094700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>978400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1050300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>889500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>833500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>763900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>650500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>603300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>524200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>236400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>553900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>510500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>399700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>326000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>458300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>470000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>449800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>410400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>390800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>382000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>370000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>363800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>352400</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>267400</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E22" s="3">
         <v>70400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>69700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>71100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>73100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>71900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>75000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>82200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>82800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>80000</v>
-      </c>
-      <c r="M22" s="3">
-        <v>74200</v>
       </c>
       <c r="N22" s="3">
         <v>74200</v>
       </c>
       <c r="O22" s="3">
+        <v>74200</v>
+      </c>
+      <c r="P22" s="3">
         <v>73500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>74800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>74300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>74400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>44200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>40000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>37900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>38300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>40000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>39100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>38900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>39400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>40200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>39200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>40500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>40400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>40500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>31200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>26500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>26400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>28300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>28100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>27400</v>
-      </c>
-      <c r="AL22" s="3">
-        <v>30600</v>
       </c>
       <c r="AM22" s="3">
         <v>30600</v>
       </c>
       <c r="AN22" s="3">
+        <v>30600</v>
+      </c>
+      <c r="AO22" s="3">
         <v>30500</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>30600</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>30700</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1549400</v>
+      </c>
+      <c r="E23" s="3">
         <v>1416800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1330300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1309500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1328800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1264400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>972500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1078700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>945000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>702000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>691300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>851700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>775500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>800700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1143000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1070000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>949700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>846300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>926900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>766300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>708800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>640400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>527400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>483800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>405100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>115200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>424900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>371500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>231300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>221400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>416000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>427600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>406500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>366000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>347300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>336200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>325000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>319100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>306800</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>222200</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>186300</v>
+      </c>
+      <c r="E24" s="3">
         <v>215800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>184600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>188400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>126000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>176000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>148000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>132800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>108600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>108700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>110300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>90900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>102800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>164200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>44000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>144300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>115600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>209400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-302100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>75800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>73200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>70400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>63700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>37200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>44600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>25100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>13200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>28700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>47200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>51400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>112900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>55100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>39600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>55200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>68900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>65600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>68600</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>44100</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1363100</v>
+      </c>
+      <c r="E26" s="3">
         <v>1201000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1145700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1121000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1202800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1088400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>824500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>945900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>836400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>601500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>582500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>741400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>684700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>697800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>978800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1026100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>805400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>730700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>717500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1068500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>633100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>567200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>457000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>420100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>410300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>78000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>380300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>346400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>218100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>192600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>368800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>376100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>293600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>310900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>307700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>280900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>256200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>253600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>238300</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>178100</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1363100</v>
+      </c>
+      <c r="E27" s="3">
         <v>1201000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1145700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1121000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1202800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1088400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>824500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>945900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>836400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>601500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>582500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>741400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>684700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>697800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>978800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1026000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>805400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>730600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>717400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1068400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>633000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>567500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>457300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>420600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>411300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>78500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>380600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>346500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>218600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>192700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>368800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>376100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>293600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>310900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>307700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>280900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>256200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>253600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>238300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>178100</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3218,8 +3279,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>10</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>10</v>
@@ -3236,29 +3297,29 @@
       <c r="AD29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-800</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>300</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>19800</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>55200</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-442000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>10</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-73300</v>
+      </c>
+      <c r="E32" s="3">
         <v>47600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>43200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>43300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-130200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>35900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>44500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>40900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-110000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>45600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>32200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>26800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-46300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>15100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-18100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-47000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-19400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>8700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>14100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-29000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-7300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>7900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-9300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-9200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-10000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-11300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-8300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-8500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-6700</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-5500</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-3700</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1363100</v>
+      </c>
+      <c r="E33" s="3">
         <v>1201000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1145700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1121000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1202800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1088400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>824500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>945900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>836400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>601500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>582500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>741400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>684700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>697800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>978800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1026000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>805400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>730600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>717400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1068400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>633000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>567500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>457300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>420600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>411300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>78500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>380600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>346500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>217800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>192700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>369100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>395900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>348800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>306900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-134300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>280900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>256200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>253600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>238300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>178100</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1363100</v>
+      </c>
+      <c r="E35" s="3">
         <v>1201000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1145700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1121000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1202800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1088400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>824500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>945900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>836400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>601500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>582500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>741400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>684700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>697800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>978800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1026000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>805400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>730600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>717400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1068400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>633000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>567500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>457300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>420600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>411300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>78500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>380600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>346500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>217800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>192700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>369100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>395900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>348800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>306900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-134300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>280900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>256200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>253600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>238300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>178100</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,740 +4305,759 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1649800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1787000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2452100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1946200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2078900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1858000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1838300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1977200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1977100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1848200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1665100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1711600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1927900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1568500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1571500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1819300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1584900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1415200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1657100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1509600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1434600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1452200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1431500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1215800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1234400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>946200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>939900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>988300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1016000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1092200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1794000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1649500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1404400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1255700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1073400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1320700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1153100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>955800</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>937000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>966300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3252600</v>
+      </c>
+      <c r="E42" s="3">
         <v>3170900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2755300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2737400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2415700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2170600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1942100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2652500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2526900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2446100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1677900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1637800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1315300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1321700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1294900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1134200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1123100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1162700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1153400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1115200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1059900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>990600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>865100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>827600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>746100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>688400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>737700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>763200</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>723400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>805100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>900100</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1130800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1477800</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1635400</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1688000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1738100</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1867400</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1752200</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>1659400</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>1528400</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3020900</v>
+      </c>
+      <c r="E43" s="3">
         <v>2405400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2166700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2401400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2369000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2258900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2417300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2024600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1902300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1712900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1944800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1724000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1870500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2065100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2435200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2002400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2016300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1769800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1862800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1582700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1465400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1355500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1351300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1151400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1264100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1247500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1302000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1181100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1136000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1084000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>693600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>620900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>675100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>732200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>749900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>687100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>593200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>805200</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>711500</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>684500</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3648500</v>
+      </c>
+      <c r="E44" s="3">
         <v>3437000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3282600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3297400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3212100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3155800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3046300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3109800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3034800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3007100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3038600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3007700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2876800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2749700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2535400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2408300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2146900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1982300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1829400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1715300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1575400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1450600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1420600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1394200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1311000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1264100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1251400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1254200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1262500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1317300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1006000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>993500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>931800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>858900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>788000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>762400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>733000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>696800</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>671200</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>703300</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>585400</v>
+      </c>
+      <c r="E45" s="3">
         <v>377100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>452600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>389900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>422000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>322500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>384600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>346000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>465100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>398500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>296600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>229200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>260400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>295600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>279700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>297700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>252700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>198800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>221800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>161000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>156400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>154500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>165600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>168000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>172300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>146500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>168900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>177200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>144100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>91900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>126300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>59800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>58300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>54800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>51200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>45400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>43300</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>52500</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>46700</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12381800</v>
+      </c>
+      <c r="E46" s="3">
         <v>11351000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11263800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10901200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10698800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9945000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9772600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10228400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10031100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9528100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8748700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>8430800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8372000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8018800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8132600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7643900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7168900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6582700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6701500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6144700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5696200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5405200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5223000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4754700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4723500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4318500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4377400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4355700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4315100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4442600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4485500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4521000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4549000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4540500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4354000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4559500</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>4392100</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4253300</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>4031600</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>3929200</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4995,8 +5100,8 @@
       <c r="P47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5073,252 +5178,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1715600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1696100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1639200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1571400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1522500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1466700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1423000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1368800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1341800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1347400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1323900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1278000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1240500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1185300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1096700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1039000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>976400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>910100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>815000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>798200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>765900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>730100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>697600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>660600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>620600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>595800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>593600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>581200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>448800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>411900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>306400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>291200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>286300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>284500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>281600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>279900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>284000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>285700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>280000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>272400</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2044600</v>
+      </c>
+      <c r="E49" s="3">
         <v>2089200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2138600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2188400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2237000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2283100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2333900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2627700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2684500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2743300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2872400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3150800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3214100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3278800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3343900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3410300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3514500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3570100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3147800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3198900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3196500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3248800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3335300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3386300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3436800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3481000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3792200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3812900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3772500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3867200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>384300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>385600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>374000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>365400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>366600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>367400</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>368500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>337300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>337700</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>338300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>535600</v>
+        <v>772300</v>
       </c>
       <c r="E52" s="3">
+        <v>613900</v>
+      </c>
+      <c r="F52" s="3">
         <v>534500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>525800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>503900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>470200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>470000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>475200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>460900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>459100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>433300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>406800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>428800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>416900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1155900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1030500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>937300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>954800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1016000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1004800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>612500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>555200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>558800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>518400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>499000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>450700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>487400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>479600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>472100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>465900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>429100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>447300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>429300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>407800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>405100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>483600</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>487600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>448100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>445100</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>456300</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17951500</v>
+      </c>
+      <c r="E54" s="3">
         <v>16873500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16720200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16318000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16067900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15188300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15001700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15681700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15433600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14957300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14280500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14136800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14072400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13683500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13729100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13123700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12597100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>12017800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>11680200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>11146500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10271100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9939200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9814600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9320100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>9280000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>8845900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9250700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9229400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9008500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>9187600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5605300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5645100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5638600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5598200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5407300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>5690400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>5532200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>5324400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>5094500</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>4996100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,186 +6145,190 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>623700</v>
+      </c>
+      <c r="E57" s="3">
         <v>515000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>425200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>429800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>458500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>429300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>432900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>376500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>359500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>354700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>376700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>363700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>371000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>410900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>530400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>479700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>443300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>424100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>379900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>380800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>342100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>295100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>262500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>254500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>264300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>243200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>256600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>221400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>202400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>206200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>152500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>154900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>169400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>169500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>149800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>138700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>147400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>139500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>116200</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>105100</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>52900</v>
+      </c>
+      <c r="E58" s="3">
         <v>51100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>51000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>46800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>45200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>43500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>40600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>790400</v>
-      </c>
-      <c r="K58" s="3">
-        <v>786300</v>
       </c>
       <c r="L58" s="3">
         <v>786300</v>
       </c>
       <c r="M58" s="3">
+        <v>786300</v>
+      </c>
+      <c r="N58" s="3">
         <v>785300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>35500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>34000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>33500</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>10</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
       <c r="U58" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="V58" s="3">
         <v>20000</v>
@@ -6208,12 +6342,12 @@
       <c r="Y58" s="3">
         <v>20000</v>
       </c>
-      <c r="Z58" s="3" t="s">
+      <c r="Z58" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AA58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
       <c r="AB58" s="3">
         <v>0</v>
       </c>
@@ -6221,7 +6355,7 @@
         <v>0</v>
       </c>
       <c r="AD58" s="3">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="AE58" s="3">
         <v>250000</v>
@@ -6232,12 +6366,12 @@
       <c r="AG58" s="3">
         <v>250000</v>
       </c>
-      <c r="AH58" s="3" t="s">
+      <c r="AH58" s="3">
+        <v>250000</v>
+      </c>
+      <c r="AI58" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AI58" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
@@ -6245,7 +6379,7 @@
         <v>0</v>
       </c>
       <c r="AL58" s="3">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="AM58" s="3">
         <v>250000</v>
@@ -6256,499 +6390,514 @@
       <c r="AO58" s="3">
         <v>250000</v>
       </c>
-      <c r="AP58" s="3" t="s">
+      <c r="AP58" s="3">
+        <v>250000</v>
+      </c>
+      <c r="AQ58" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2611000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2291800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2474200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2649500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2703100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2596800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2672700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2754900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2711400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2493800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2505300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2631700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2603700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2226500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2952100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2659700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2427700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2404900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2376200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2122200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1741100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1714400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1737600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1494400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1435500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1410000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1461600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1472100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1316100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1244600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1080100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1156000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1044900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1031000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1016700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1077400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>895800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>859800</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>821600</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>869700</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4304900</v>
+      </c>
+      <c r="E60" s="3">
         <v>3751600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3982500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4050000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4085800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3909900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4138300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4798200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4660800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4458500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4571000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3817700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3742800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3418500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3482500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3139400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2871100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2829000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2776100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2523000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2103200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2029500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2020100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1748800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1699800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1653300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1718200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1943400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1768500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1700900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1482500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1310900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1214300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1200400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1166500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1466000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1293200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1249200</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1187700</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>974700</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6098800</v>
+      </c>
+      <c r="E61" s="3">
         <v>6094200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6058500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6041400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6043100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6045700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6032000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6035700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6033300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6037400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5298900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6030400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6029100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6027600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6113700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6312700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6660700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3699800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3424100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3423400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3422800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3422100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3441500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3420400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3469700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3443900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3399900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3174100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3173400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3172600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1988400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2237900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2237400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2461900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2486400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2524800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2680500</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2704900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2729200</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>3018600</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>439300</v>
+      </c>
+      <c r="E62" s="3">
         <v>443800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>434100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>431100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>392200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>388000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>379800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>368300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>438400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>433300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>415700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>396300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>454200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>444800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1529600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1569500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1666200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1410400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1433300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1340900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1369500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1374800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1402800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1388500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1429500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1423500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1444600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1432200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1389000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1428500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>536700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>528900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>566400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>565700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>528700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>235600</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>232100</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>223100</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>212400</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>221300</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11601700</v>
+      </c>
+      <c r="E66" s="3">
         <v>11043000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11254500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11332900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11375500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11183600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11417100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>12122000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12065200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11862400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11236800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11146600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11152600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11000800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11125800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11021600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11195700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7937500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7631700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7285500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6893600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6824400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6879500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6572900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6614500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6538500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6581000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6568200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6349400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6338500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4007700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4077700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4018100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4228000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4181600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>4226400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>4205800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>4177100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>4129400</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>4214600</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3683900</v>
+      </c>
+      <c r="E72" s="3">
         <v>3187500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2860600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2495300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2179300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1646100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1284600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1328200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1137300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>958900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>921500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>966200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>848400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>721300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>670000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1119000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>366900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1972600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1944000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1801300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1277100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1070100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>903700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>753900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>654900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>376700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>719000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>733200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>714800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>928100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1048800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1027400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1056400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>862700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>729500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>996500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>848500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>702300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>534200</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>381100</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6349800</v>
+      </c>
+      <c r="E76" s="3">
         <v>5830500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5465700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4985100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4692500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4004700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3584500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3559700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3368300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3094900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3043700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2990200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2919800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2682800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2603300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2102100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1401400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4080300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4048500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3860900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3377600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3114900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2935200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2747200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2665400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2307400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2669800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2661200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2659100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2849100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1597600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1567400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1620500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1370100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1225600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1464000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1326400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1147300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>965100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>781500</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1363100</v>
+      </c>
+      <c r="E81" s="3">
         <v>1201000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1145700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1121000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1202800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1088400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>824500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>945900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>836400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>601500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>582500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>741400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>684700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>697800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>978800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1026000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>805400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>730600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>717400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1068400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>633000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>567500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>457300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>420600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>411300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>78500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>380600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>346500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>217800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>192700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>369100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>395900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>348800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>306900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-134300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>280900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>256200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>253600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>238300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>178100</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E83" s="3">
         <v>44200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>45100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>39000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>42100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>41600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>39700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>39100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>40200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>39700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>37900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>36700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>36600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>34400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>103500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>101900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>100800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>92100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>85500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>84800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>84600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>84400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>84300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>80100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>78900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>82000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>88500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>98600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>127900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>73400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>15800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>16100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>15000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>16300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>16100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>15300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>14300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>14200</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>14900</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>906400</v>
+      </c>
+      <c r="E89" s="3">
         <v>707500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1367600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1161600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1165000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1072200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>849500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>995200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>892600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>910000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>622200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>883700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>959100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1010900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>688300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1011500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>819200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>818900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>810800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>863800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>465600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>646200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>561100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>512200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>452800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>442000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>387700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>496200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>325500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>163600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>282200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>381400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>373500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>352600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>129400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>373600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>462600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>224800</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>222400</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>169800</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-89300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-85200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-105600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-95900</v>
       </c>
-      <c r="G91" s="3">
-        <v>-105400</v>
-      </c>
       <c r="H91" s="3">
+        <v>-100400</v>
+      </c>
+      <c r="I91" s="3">
         <v>-82100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-92300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-60400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-60700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-71800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-76800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-68000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-78700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-84900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-93600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-84400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-73200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-64900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-69000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-55400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-61200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-59100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-55900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-41800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-43400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-34900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-32600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-55800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-26000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-26400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-22800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-15000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-13400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-15800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-10700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-9400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-9900</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-173100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-494300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-112700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-410000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-325300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-319800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>613700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-171000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-138800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-858000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-88500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-391700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-74500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-113200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-241400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-53500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-25400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-569500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-106300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-175300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-93600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-176600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-95900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-134300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-105800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>1800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-8100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-146700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>30400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1734900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>208600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>314900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>126800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>25900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>26000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>113000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-154400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-98400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-140300</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-167800</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>305300</v>
+      </c>
+      <c r="E96" s="3">
         <v>248800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>249700</v>
-      </c>
-      <c r="F96" s="3">
-        <v>254000</v>
       </c>
       <c r="G96" s="3">
         <v>254000</v>
       </c>
       <c r="H96" s="3">
+        <v>254000</v>
+      </c>
+      <c r="I96" s="3">
         <v>225800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>226800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>198100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>197500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>197200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>196900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>181500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>179500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>180900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-184200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-188000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-157600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-159000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-159100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-162800</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-139300</v>
       </c>
       <c r="X96" s="3">
         <v>-139300</v>
       </c>
       <c r="Y96" s="3">
+        <v>-139300</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-139600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-141200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-132800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-133300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-134700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-121600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-121400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-113600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-114600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-122800</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-117000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-92100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-92600</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-100300</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-84600</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-85500</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-84500</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-89300</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-877100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-879200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-747600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-881800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-629800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-735200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1583000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-837700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-618900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>138900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-590900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-705200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-511300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-902700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-710500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-705700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-603700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-486400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-557800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-609000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-392800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-439500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-261400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-404200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-61400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-432600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-432000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-373600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-432100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>869300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-347500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-449700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-341400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-202300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-406300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-320100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-113000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-112200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-100900</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-146700</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E101" s="3">
         <v>2600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-19200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>13600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-7700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>10600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-14000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>2100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>15800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-18000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-20400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>15800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-18000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-20400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-4500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>3300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>11800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>7800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>2600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-4900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-10200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>6100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>3700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1200</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>1900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>4500</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-10500</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-137200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-665100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>505900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-132700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>220900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>19700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-138900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>129000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>183100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-46500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-216300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>359400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-247800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>234400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>169700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-241900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>147500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>75000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-17500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>20700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>215600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-18600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>288200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-48500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-27600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-76200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-701800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>144500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>245100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>148700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>182300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-247300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>167600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>197200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>18800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-29300</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-142200</v>
       </c>
     </row>
